--- a/EG1B.xlsx
+++ b/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
   <si>
     <t/>
   </si>
   <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
+    <t>20099547</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 1500</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -31,157 +31,208 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
+    <t>20036200</t>
+  </si>
+  <si>
+    <t>SPRITE SOFT DRINK 1L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20036199</t>
+  </si>
+  <si>
+    <t>FANTA STRAWBERRY 1 L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20036197</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 1 LT</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>IDM MINERAL 600 ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20142863</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 380</t>
+  </si>
+  <si>
+    <t>20142862</t>
+  </si>
+  <si>
+    <t>EWATER GRPFRT 380</t>
+  </si>
+  <si>
+    <t>20128821</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO 390ML</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20143469</t>
+  </si>
+  <si>
+    <t>GJAH K/TBRK GL BT200</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20090314</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT F/C200ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM CO 200 ML</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM ST 200 ML</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20143944</t>
+  </si>
+  <si>
+    <t>PTOS KRN HNY BTR105</t>
+  </si>
+  <si>
+    <t>10002101</t>
+  </si>
+  <si>
+    <t>HAPPYTOS CHP M 140 G</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20089542</t>
-  </si>
-  <si>
-    <t>IDM AIR MN 8+ BTL500</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>20143469</t>
-  </si>
-  <si>
-    <t>GJAH K/TBRK GL BT200</t>
-  </si>
-  <si>
-    <t>20143447</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH ORI 300</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20143446</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR300</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20142910</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 900</t>
-  </si>
-  <si>
-    <t>10000752</t>
-  </si>
-  <si>
-    <t>TARO SNACK BARBQ 32G</t>
-  </si>
-  <si>
-    <t>20101065</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHKN 50</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10006890</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 40G</t>
-  </si>
-  <si>
-    <t>10035883</t>
-  </si>
-  <si>
-    <t>GARUDA PILUS PDS 80G</t>
-  </si>
-  <si>
-    <t>20143335</t>
-  </si>
-  <si>
-    <t>MI KRMZ SHR AY PGG4S</t>
-  </si>
-  <si>
-    <t>20142997</t>
-  </si>
-  <si>
-    <t>SNICKERS CHOCO FB</t>
-  </si>
-  <si>
-    <t>20099762</t>
-  </si>
-  <si>
-    <t>NYAM2 POPSTIX CHO 48</t>
-  </si>
-  <si>
-    <t>20124895</t>
-  </si>
-  <si>
-    <t>G/T COKIES CHOCDIP71</t>
+    <t>20056977</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA BWG 90</t>
+  </si>
+  <si>
+    <t>10029724</t>
+  </si>
+  <si>
+    <t>GARUDA KCNG ATOM 95</t>
+  </si>
+  <si>
+    <t>20023148</t>
+  </si>
+  <si>
+    <t>TIC TAC SAPI PNGG 80</t>
+  </si>
+  <si>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
+  </si>
+  <si>
+    <t>20093909</t>
+  </si>
+  <si>
+    <t>REBO KUACI MILK 120</t>
+  </si>
+  <si>
+    <t>20068536</t>
+  </si>
+  <si>
+    <t>REBO KUACI G.TEA 120</t>
+  </si>
+  <si>
+    <t>10003507</t>
+  </si>
+  <si>
+    <t>MR.P KCANG MADU 80 G</t>
+  </si>
+  <si>
+    <t>20143939</t>
+  </si>
+  <si>
+    <t>IDM KCANG METE ORI65</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20143054</t>
+  </si>
+  <si>
+    <t>FOXS GUM EMOTIS 50</t>
+  </si>
+  <si>
+    <t>20143892</t>
+  </si>
+  <si>
+    <t>CMPH MLW PFF N/CHO40</t>
   </si>
   <si>
     <t>20020008</t>
@@ -215,27 +266,6 @@
   </si>
   <si>
     <t>MILO DRNK EXT CHO3+1</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20143393</t>
-  </si>
-  <si>
-    <t>I/P SPGT FR CKN CB80</t>
-  </si>
-  <si>
-    <t>20138739</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI BGLN 84G</t>
-  </si>
-  <si>
-    <t>20138738</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI CRBO 80G</t>
   </si>
 </sst>
 </file>
@@ -628,13 +658,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -715,27 +746,27 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -749,21 +780,21 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -772,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -780,10 +811,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -792,7 +823,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -800,10 +831,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -812,10 +843,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,19 +863,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
@@ -852,47 +883,47 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -900,19 +931,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -920,22 +951,22 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -949,13 +980,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -969,10 +1000,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -980,16 +1011,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -1000,36 +1031,36 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>12</v>
@@ -1040,76 +1071,76 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
@@ -1120,16 +1151,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>12</v>
@@ -1140,102 +1171,182 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/EG1B.xlsx
+++ b/EG1B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
   <si>
     <t/>
   </si>
   <si>
-    <t>20099547</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 1500</t>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
   </si>
   <si>
     <t>EG1B</t>
@@ -28,135 +28,108 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20130447</t>
+  </si>
+  <si>
+    <t>TSTS TRTL CHP R/C130</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20036200</t>
-  </si>
-  <si>
-    <t>SPRITE SOFT DRINK 1L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20036199</t>
-  </si>
-  <si>
-    <t>FANTA STRAWBERRY 1 L</t>
+    <t>20087713</t>
+  </si>
+  <si>
+    <t>IDM NDL AYM PDS 90G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20036197</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 1 LT</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>IDM AIR MINE BTL 1 L</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>IDM MINERAL 600 ML</t>
+    <t>20127276</t>
+  </si>
+  <si>
+    <t>LWK KOPI MURNI 9'S</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20125638</t>
+  </si>
+  <si>
+    <t>NTRSARI JRK PRS 10'S</t>
+  </si>
+  <si>
+    <t>20122808</t>
+  </si>
+  <si>
+    <t>MAMAKOKO SANTAN 65ML</t>
+  </si>
+  <si>
+    <t>20059240</t>
+  </si>
+  <si>
+    <t>ANTANGIN JUNIOR 5'S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20142863</t>
-  </si>
-  <si>
-    <t>EWATER LEMON 380</t>
-  </si>
-  <si>
-    <t>20142862</t>
-  </si>
-  <si>
-    <t>EWATER GRPFRT 380</t>
-  </si>
-  <si>
-    <t>20128821</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO 390ML</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
+    <t>20134048</t>
+  </si>
+  <si>
+    <t>HILO PRTEIN CHOCO190</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20143469</t>
-  </si>
-  <si>
-    <t>GJAH K/TBRK GL BT200</t>
+    <t>20133371</t>
+  </si>
+  <si>
+    <t>MLTON PSTL BCRNT16.5</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20090314</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT F/C200ML</t>
+    <t>20131699</t>
+  </si>
+  <si>
+    <t>EMCO PKEMON FACE OFF</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM CO 200 ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM ST 200 ML</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20143944</t>
   </si>
   <si>
@@ -169,9 +142,6 @@
     <t>HAPPYTOS CHP M 140 G</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
     <t>20056977</t>
   </si>
   <si>
@@ -218,9 +188,6 @@
   </si>
   <si>
     <t>IDM KCANG METE ORI65</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20143054</t>
@@ -658,15 +625,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -746,15 +712,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -763,27 +729,27 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>19</v>
@@ -803,10 +769,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -823,10 +789,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -843,18 +809,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -863,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>9</v>
@@ -871,10 +837,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -883,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
@@ -891,10 +857,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -903,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>9</v>
@@ -911,10 +877,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -923,7 +889,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -931,62 +897,62 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,21 +966,21 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1023,330 +989,250 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
